--- a/releases/v1.0.0-rc1/testing-criteria-scorecard-v1.0.0-rc1.xlsx
+++ b/releases/v1.0.0-rc1/testing-criteria-scorecard-v1.0.0-rc1.xlsx
@@ -1800,7 +1800,7 @@
     <row r="3" ht="42" customHeight="1" s="125">
       <c r="B3" s="128" t="inlineStr">
         <is>
-          <t>DRAFT — Version v1.0.0-rc1 · commit 5d656dc (built 2026-10-15 01:36 UTC). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
+          <t>DRAFT — Version v1.0.0-rc1 · commit 5d656dc (built 2026-10-15 03:16 UTC). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 01:36 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7375,7 +7375,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 01:36 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -12354,7 +12354,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 01:36 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -14485,7 +14485,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 01:36 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -27254,7 +27254,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 01:36 UTC&amp;C&amp;"Arial,Regular"&amp;7 HIE System Validation Testing Criteria — Printed Evaluation Report&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;C&amp;"Arial,Regular"&amp;7 HIE System Validation Testing Criteria — Printed Evaluation Report&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -28558,7 +28558,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 01:36 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -29148,7 +29148,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 01:36 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -32450,7 +32450,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 01:36 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -33630,7 +33630,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 01:36 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -35123,7 +35123,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 01:36 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -37289,7 +37289,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 01:36 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -42560,7 +42560,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 01:36 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -46768,7 +46768,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 01:36 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/releases/v1.0.0-rc1/testing-criteria-scorecard-v1.0.0-rc1.xlsx
+++ b/releases/v1.0.0-rc1/testing-criteria-scorecard-v1.0.0-rc1.xlsx
@@ -1800,7 +1800,7 @@
     <row r="3" ht="42" customHeight="1" s="125">
       <c r="B3" s="128" t="inlineStr">
         <is>
-          <t>DRAFT — Version v1.0.0-rc1 · commit 5d656dc (built 2026-10-15 03:16 UTC). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
+          <t>DRAFT — Version v1.0.0-rc1 · commit 5d656dc (built 2026-10-15 04:26 UTC). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 04:26 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7375,7 +7375,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 04:26 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -12354,7 +12354,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 04:26 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -14485,7 +14485,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 04:26 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -27254,7 +27254,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;C&amp;"Arial,Regular"&amp;7 HIE System Validation Testing Criteria — Printed Evaluation Report&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 04:26 UTC&amp;C&amp;"Arial,Regular"&amp;7 HIE System Validation Testing Criteria — Printed Evaluation Report&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -28558,7 +28558,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 04:26 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -29148,7 +29148,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 04:26 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -32450,7 +32450,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 04:26 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -33630,7 +33630,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 04:26 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -35123,7 +35123,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 04:26 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -37289,7 +37289,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 04:26 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -42560,7 +42560,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 04:26 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -46768,7 +46768,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 03:16 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
+    <oddFooter>&amp;L&amp;8 Version v1.0.0-rc1 · commit 5d656dc · built 2026-10-15 04:26 UTC&amp;R&amp;8 © DOH WV CHD · CC BY 4.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
